--- a/data/DRF/RR_raw_extraction.xlsx
+++ b/data/DRF/RR_raw_extraction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/steps/data/DRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125A532E-57B5-6C43-8030-A5815417B75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8CA99A-02AE-5C47-B13F-BE7A484868A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="640" yWindow="1000" windowWidth="27240" windowHeight="15100" xr2:uid="{C1C0BADF-3E30-0047-98DE-A4D988F71C08}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -107,6 +107,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -128,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -139,6 +145,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1826,19 +1833,19 @@
                   <c:v>1.0002312200000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.99693434999999997</c:v>
+                  <c:v>0.99477459000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0024416300000001</c:v>
+                  <c:v>0.99810295999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0079876699999999</c:v>
+                  <c:v>1.003625</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0090966699999999</c:v>
+                  <c:v>1.0003806200000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0102068799999999</c:v>
+                  <c:v>1.0080183700000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8524,7 +8531,7 @@
       <c r="B25">
         <v>1.0259182922177299</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="6">
         <v>1.0487879899999999</v>
       </c>
       <c r="D25">
@@ -8538,7 +8545,7 @@
       <c r="B26">
         <v>1.0002312183081601</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="6">
         <v>1.0002312200000001</v>
       </c>
       <c r="D26">
@@ -8552,8 +8559,8 @@
       <c r="B27">
         <v>0.97519536320376099</v>
       </c>
-      <c r="C27" s="3">
-        <v>0.99693434999999997</v>
+      <c r="C27" s="6">
+        <v>0.99477459000000001</v>
       </c>
       <c r="D27">
         <v>0.94973339637425103</v>
@@ -8566,8 +8573,8 @@
       <c r="B28">
         <v>0.95077829650273804</v>
       </c>
-      <c r="C28" s="3">
-        <v>1.0024416300000001</v>
+      <c r="C28" s="6">
+        <v>0.99810295999999998</v>
       </c>
       <c r="D28">
         <v>0.89780999806166695</v>
@@ -8580,8 +8587,8 @@
       <c r="B29">
         <v>0.92698025137881301</v>
       </c>
-      <c r="C29" s="3">
-        <v>1.0079876699999999</v>
+      <c r="C29" s="6">
+        <v>1.003625</v>
       </c>
       <c r="D29">
         <v>0.85248302907414297</v>
@@ -8594,8 +8601,8 @@
       <c r="B30">
         <v>0.90377040083759597</v>
       </c>
-      <c r="C30" s="3">
-        <v>1.0090966699999999</v>
+      <c r="C30" s="6">
+        <v>1.0003806200000001</v>
       </c>
       <c r="D30">
         <v>0.80943775199485601</v>
@@ -8608,8 +8615,8 @@
       <c r="B31">
         <v>0.88503558294390094</v>
       </c>
-      <c r="C31" s="3">
-        <v>1.0102068799999999</v>
+      <c r="C31" s="6">
+        <v>1.0080183700000001</v>
       </c>
       <c r="D31">
         <v>0.76856600308638201</v>

--- a/data/DRF/RR_raw_extraction.xlsx
+++ b/data/DRF/RR_raw_extraction.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/steps/data/DRF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/data/DRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8CA99A-02AE-5C47-B13F-BE7A484868A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB6EA33-7FF8-6D43-A29E-4923EE498195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="640" yWindow="1000" windowWidth="27240" windowHeight="15100" xr2:uid="{C1C0BADF-3E30-0047-98DE-A4D988F71C08}"/>
+    <workbookView xWindow="32600" yWindow="-2520" windowWidth="31000" windowHeight="18960" xr2:uid="{C1C0BADF-3E30-0047-98DE-A4D988F71C08}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1687,29 +1687,14 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$25:$A$31</c:f>
+              <c:f>Feuil1!$A$25:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
@@ -1717,29 +1702,14 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$B$25:$B$31</c:f>
+              <c:f>Feuil1!$B$25:$B$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>1.0259182922177299</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0002312183081601</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.97519536320376099</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.95077829650273804</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.92698025137881301</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.90377040083759597</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>0.88503558294390094</c:v>
                 </c:pt>
               </c:numCache>
@@ -1792,29 +1762,14 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$25:$A$31</c:f>
+              <c:f>Feuil1!$A$25:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
@@ -1822,29 +1777,14 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$C$25:$C$31</c:f>
+              <c:f>Feuil1!$C$25:$C$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>1.0487879899999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0002312200000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.99477459000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.99810295999999998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.003625</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.0003806200000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>1.0080183700000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -1897,29 +1837,14 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$25:$A$31</c:f>
+              <c:f>Feuil1!$A$25:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
@@ -1927,29 +1852,14 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$D$25:$D$31</c:f>
+              <c:f>Feuil1!$D$25:$D$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0.99913196969009099</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0002312183081601</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.94973339637425103</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.89780999806166695</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.85248302907414297</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.80943775199485601</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>0.76856600308638201</c:v>
                 </c:pt>
               </c:numCache>
@@ -2359,7 +2269,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$B$34</c:f>
+              <c:f>Feuil1!$B$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2394,29 +2304,14 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$35:$A$41</c:f>
+              <c:f>Feuil1!$A$30:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
@@ -2424,29 +2319,14 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$B$35:$B$41</c:f>
+              <c:f>Feuil1!$B$30:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>1.0587103499999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.98734633000000005</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.93292032999999996</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.87765811000000005</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.82566938999999995</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.77676025999999998</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>0.73074828999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -2464,7 +2344,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$C$34</c:f>
+              <c:f>Feuil1!$C$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2499,29 +2379,14 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$35:$A$41</c:f>
+              <c:f>Feuil1!$A$30:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
@@ -2529,29 +2394,14 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$C$35:$C$41</c:f>
+              <c:f>Feuil1!$C$30:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>1.12047486923464</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.98734633487204804</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.99166216992258405</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.99166216992258405</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.98734633487204804</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.98734633487204804</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>0.98304928286350901</c:v>
                 </c:pt>
               </c:numCache>
@@ -2569,7 +2419,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$D$34</c:f>
+              <c:f>Feuil1!$D$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2604,29 +2454,14 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$35:$A$41</c:f>
+              <c:f>Feuil1!$A$30:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7999.99999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
@@ -2634,29 +2469,14 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$D$35:$D$41</c:f>
+              <c:f>Feuil1!$D$30:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0.99599687000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.98734633000000005</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.87765811000000005</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.78015559000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.68746187999999997</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.60842947999999997</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>0.54083663999999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -3061,7 +2881,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$B$44</c:f>
+              <c:f>Feuil1!$B$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3096,7 +2916,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$45:$A$51</c:f>
+              <c:f>Feuil1!$A$35:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3126,7 +2946,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$B$45:$B$51</c:f>
+              <c:f>Feuil1!$B$35:$B$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3166,7 +2986,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$C$44</c:f>
+              <c:f>Feuil1!$C$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3201,7 +3021,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$45:$A$51</c:f>
+              <c:f>Feuil1!$A$35:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3231,7 +3051,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$C$45:$C$51</c:f>
+              <c:f>Feuil1!$C$35:$C$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3271,7 +3091,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$D$44</c:f>
+              <c:f>Feuil1!$D$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3306,7 +3126,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$45:$A$51</c:f>
+              <c:f>Feuil1!$A$35:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3336,7 +3156,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$D$45:$D$51</c:f>
+              <c:f>Feuil1!$D$35:$D$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3763,7 +3583,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$B$54</c:f>
+              <c:f>Feuil1!$B$44</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3798,29 +3618,14 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$55:$A$61</c:f>
+              <c:f>Feuil1!$A$45:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
@@ -3828,29 +3633,14 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$B$55:$B$61</c:f>
+              <c:f>Feuil1!$B$45:$B$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>1.0988227370000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.99029234399999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.89691209999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.81636997</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.73210290200000006</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.66636053299999998</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>0.60352564399999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -3868,7 +3658,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$C$54</c:f>
+              <c:f>Feuil1!$C$44</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3903,29 +3693,14 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$55:$A$61</c:f>
+              <c:f>Feuil1!$A$45:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
@@ -3933,29 +3708,14 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$C$55:$C$61</c:f>
+              <c:f>Feuil1!$C$45:$C$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>1.1208057360000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.99029234399999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.92396164700000005</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.86207384200000003</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.80035804200000005</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.74306047200000003</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>0.68986483099999996</c:v>
                 </c:pt>
               </c:numCache>
@@ -3973,7 +3733,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$D$54</c:f>
+              <c:f>Feuil1!$D$44</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4008,29 +3768,14 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$55:$A$61</c:f>
+              <c:f>Feuil1!$A$45:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4038,29 +3783,14 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$D$55:$D$61</c:f>
+              <c:f>Feuil1!$D$45:$D$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>1.0666540229999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.99029234399999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.87497672000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.77692706700000003</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.68306597300000005</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.60054430199999997</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>0.53061329499999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -7789,7 +7519,7 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>1143000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7821,13 +7551,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>1155700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7859,13 +7589,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>1143000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7897,13 +7627,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -8251,7 +7981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{524C558B-4776-E643-A4A5-A5B4D7116217}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" customWidth="1"/>
@@ -8540,92 +8270,70 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="B26">
-        <v>1.0002312183081601</v>
+        <v>0.88503558294390094</v>
       </c>
       <c r="C26" s="6">
-        <v>1.0002312200000001</v>
+        <v>1.0080183700000001</v>
       </c>
       <c r="D26">
-        <v>1.0002312183081601</v>
+        <v>0.76856600308638201</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>4000</v>
-      </c>
-      <c r="B27">
-        <v>0.97519536320376099</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.99477459000000001</v>
-      </c>
-      <c r="D27">
-        <v>0.94973339637425103</v>
-      </c>
-    </row>
+    <row r="27" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>6000</v>
-      </c>
-      <c r="B28">
-        <v>0.95077829650273804</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.99810295999999998</v>
-      </c>
-      <c r="D28">
-        <v>0.89780999806166695</v>
+      <c r="A28" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>8000</v>
-      </c>
-      <c r="B29">
-        <v>0.92698025137881301</v>
-      </c>
-      <c r="C29" s="6">
-        <v>1.003625</v>
-      </c>
-      <c r="D29">
-        <v>0.85248302907414297</v>
+      <c r="A29" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>10000</v>
-      </c>
-      <c r="B30">
-        <v>0.90377040083759597</v>
-      </c>
-      <c r="C30" s="6">
-        <v>1.0003806200000001</v>
-      </c>
-      <c r="D30">
-        <v>0.80943775199485601</v>
+        <v>0</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1.0587103499999999</v>
+      </c>
+      <c r="C30">
+        <v>1.12047486923464</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.99599687000000003</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>12000</v>
       </c>
-      <c r="B31">
-        <v>0.88503558294390094</v>
-      </c>
-      <c r="C31" s="6">
-        <v>1.0080183700000001</v>
-      </c>
-      <c r="D31">
-        <v>0.76856600308638201</v>
+      <c r="B31" s="3">
+        <v>0.73074828999999997</v>
+      </c>
+      <c r="C31">
+        <v>0.98304928286350901</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.54083663999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:4" ht="92" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -8643,107 +8351,107 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35">
+      <c r="A35" s="3">
         <v>0</v>
       </c>
-      <c r="B35" s="3">
-        <v>1.0587103499999999</v>
+      <c r="B35">
+        <v>1.23182733947379</v>
       </c>
       <c r="C35">
-        <v>1.12047486923464</v>
-      </c>
-      <c r="D35" s="3">
-        <v>0.99599687000000003</v>
+        <v>1.32994635834779</v>
+      </c>
+      <c r="D35">
+        <v>1.1461024791234</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>1999.99999999999</v>
-      </c>
-      <c r="B36" s="3">
-        <v>0.98734633000000005</v>
+      <c r="A36" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B36">
+        <v>0.98767208497389603</v>
       </c>
       <c r="C36">
-        <v>0.98734633487204804</v>
-      </c>
-      <c r="D36" s="3">
-        <v>0.98734633000000005</v>
+        <v>0.98767208497389603</v>
+      </c>
+      <c r="D36">
+        <v>0.98767208497389603</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>3999.99999999999</v>
-      </c>
-      <c r="B37" s="3">
-        <v>0.93292032999999996</v>
+      <c r="A37" s="3">
+        <v>4000</v>
+      </c>
+      <c r="B37">
+        <v>0.802692892265081</v>
       </c>
       <c r="C37">
-        <v>0.99166216992258405</v>
-      </c>
-      <c r="D37" s="3">
-        <v>0.87765811000000005</v>
+        <v>0.86273179572012704</v>
+      </c>
+      <c r="D37">
+        <v>0.74683219337600304</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>5999.99999999999</v>
-      </c>
-      <c r="B38" s="3">
-        <v>0.87765811000000005</v>
+      <c r="A38" s="3">
+        <v>6000</v>
+      </c>
+      <c r="B38">
+        <v>0.66422872369433394</v>
       </c>
       <c r="C38">
-        <v>0.99166216992258405</v>
-      </c>
-      <c r="D38" s="3">
-        <v>0.78015559000000001</v>
+        <v>0.75700147923349603</v>
+      </c>
+      <c r="D38">
+        <v>0.58020394448714896</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>7999.99999999999</v>
-      </c>
-      <c r="B39" s="3">
-        <v>0.82566938999999995</v>
+      <c r="A39" s="3">
+        <v>8000</v>
+      </c>
+      <c r="B39">
+        <v>0.57759413920027103</v>
       </c>
       <c r="C39">
-        <v>0.98734633487204804</v>
-      </c>
-      <c r="D39" s="3">
-        <v>0.68746187999999997</v>
+        <v>0.6886219241514</v>
+      </c>
+      <c r="D39">
+        <v>0.48446756912310301</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40">
+      <c r="A40" s="3">
         <v>10000</v>
       </c>
-      <c r="B40" s="3">
-        <v>0.77676025999999998</v>
+      <c r="B40">
+        <v>0.54717719375149798</v>
       </c>
       <c r="C40">
-        <v>0.98734633487204804</v>
-      </c>
-      <c r="D40" s="3">
-        <v>0.60842947999999997</v>
+        <v>0.65826665149219399</v>
+      </c>
+      <c r="D40">
+        <v>0.45483525662899998</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41">
+      <c r="A41" s="3">
         <v>12000</v>
       </c>
-      <c r="B41" s="3">
-        <v>0.73074828999999997</v>
+      <c r="B41">
+        <v>0.57759413920027103</v>
       </c>
       <c r="C41">
-        <v>0.98304928286350901</v>
-      </c>
-      <c r="D41" s="3">
-        <v>0.54083663999999998</v>
+        <v>0.6886219241514</v>
+      </c>
+      <c r="D41">
+        <v>0.482288393963692</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="92" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -8761,218 +8469,30 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
+      <c r="A45">
         <v>0</v>
       </c>
       <c r="B45">
-        <v>1.23182733947379</v>
+        <v>1.0988227370000001</v>
       </c>
       <c r="C45">
-        <v>1.32994635834779</v>
+        <v>1.1208057360000001</v>
       </c>
       <c r="D45">
-        <v>1.1461024791234</v>
+        <v>1.0666540229999999</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
-        <v>2000</v>
+      <c r="A46">
+        <v>12000</v>
       </c>
       <c r="B46">
-        <v>0.98767208497389603</v>
+        <v>0.60352564399999997</v>
       </c>
       <c r="C46">
-        <v>0.98767208497389603</v>
+        <v>0.68986483099999996</v>
       </c>
       <c r="D46">
-        <v>0.98767208497389603</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
-        <v>4000</v>
-      </c>
-      <c r="B47">
-        <v>0.802692892265081</v>
-      </c>
-      <c r="C47">
-        <v>0.86273179572012704</v>
-      </c>
-      <c r="D47">
-        <v>0.74683219337600304</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
-        <v>6000</v>
-      </c>
-      <c r="B48">
-        <v>0.66422872369433394</v>
-      </c>
-      <c r="C48">
-        <v>0.75700147923349603</v>
-      </c>
-      <c r="D48">
-        <v>0.58020394448714896</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
-        <v>8000</v>
-      </c>
-      <c r="B49">
-        <v>0.57759413920027103</v>
-      </c>
-      <c r="C49">
-        <v>0.6886219241514</v>
-      </c>
-      <c r="D49">
-        <v>0.48446756912310301</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
-        <v>10000</v>
-      </c>
-      <c r="B50">
-        <v>0.54717719375149798</v>
-      </c>
-      <c r="C50">
-        <v>0.65826665149219399</v>
-      </c>
-      <c r="D50">
-        <v>0.45483525662899998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
-        <v>12000</v>
-      </c>
-      <c r="B51">
-        <v>0.57759413920027103</v>
-      </c>
-      <c r="C51">
-        <v>0.6886219241514</v>
-      </c>
-      <c r="D51">
-        <v>0.482288393963692</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>0</v>
-      </c>
-      <c r="B55">
-        <v>1.0988227370000001</v>
-      </c>
-      <c r="C55">
-        <v>1.1208057360000001</v>
-      </c>
-      <c r="D55">
-        <v>1.0666540229999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>2000</v>
-      </c>
-      <c r="B56">
-        <v>0.99029234399999999</v>
-      </c>
-      <c r="C56">
-        <v>0.99029234399999999</v>
-      </c>
-      <c r="D56">
-        <v>0.99029234399999999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>4000</v>
-      </c>
-      <c r="B57">
-        <v>0.89691209999999999</v>
-      </c>
-      <c r="C57">
-        <v>0.92396164700000005</v>
-      </c>
-      <c r="D57">
-        <v>0.87497672000000004</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>6000</v>
-      </c>
-      <c r="B58">
-        <v>0.81636997</v>
-      </c>
-      <c r="C58">
-        <v>0.86207384200000003</v>
-      </c>
-      <c r="D58">
-        <v>0.77692706700000003</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>8000</v>
-      </c>
-      <c r="B59">
-        <v>0.73210290200000006</v>
-      </c>
-      <c r="C59">
-        <v>0.80035804200000005</v>
-      </c>
-      <c r="D59">
-        <v>0.68306597300000005</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>10000</v>
-      </c>
-      <c r="B60">
-        <v>0.66636053299999998</v>
-      </c>
-      <c r="C60">
-        <v>0.74306047200000003</v>
-      </c>
-      <c r="D60">
-        <v>0.60054430199999997</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>12000</v>
-      </c>
-      <c r="B61">
-        <v>0.60352564399999997</v>
-      </c>
-      <c r="C61">
-        <v>0.68986483099999996</v>
-      </c>
-      <c r="D61">
         <v>0.53061329499999998</v>
       </c>
     </row>
